--- a/players_club_weather_differences.xlsx
+++ b/players_club_weather_differences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/solomonkalumamcharo/Desktop/Desktop - Solomon’s MacBook Pro/Woolwich_Computing_Incorporated/sunnyinit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C39376-673E-D942-A7A4-71F7AC576B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{276F4A4E-74FE-F344-9BED-89E58A5CD360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="106">
   <si>
     <t>full_name</t>
   </si>
@@ -332,6 +332,12 @@
   </si>
   <si>
     <t> Mateus Gonçalo Espanha Fernandes</t>
+  </si>
+  <si>
+    <t>price_before</t>
+  </si>
+  <si>
+    <t>price_after</t>
   </si>
 </sst>
 </file>
@@ -361,7 +367,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -384,13 +390,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -695,10 +715,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH48"/>
+  <dimension ref="A1:AJ48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="27.1640625" customWidth="1"/>
+    <col min="34" max="34" width="20.6640625" customWidth="1"/>
+    <col min="35" max="35" width="11.6640625" customWidth="1"/>
+    <col min="36" max="36" width="11" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -801,8 +827,14 @@
       <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="AI1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>105</v>
+      </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -905,8 +937,14 @@
       <c r="AH2">
         <v>-213.30000000000081</v>
       </c>
+      <c r="AI2">
+        <v>516</v>
+      </c>
+      <c r="AJ2">
+        <v>350</v>
+      </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -1009,8 +1047,14 @@
       <c r="AH3">
         <v>3.7999999999993861</v>
       </c>
+      <c r="AI3">
+        <v>697</v>
+      </c>
+      <c r="AJ3">
+        <v>350</v>
+      </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -1113,8 +1157,14 @@
       <c r="AH4">
         <v>458.4000000000002</v>
       </c>
+      <c r="AI4">
+        <v>363</v>
+      </c>
+      <c r="AJ4">
+        <v>215</v>
+      </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>42</v>
       </c>
@@ -1217,8 +1267,14 @@
       <c r="AH5">
         <v>-54.300000000000182</v>
       </c>
+      <c r="AI5">
+        <v>1637</v>
+      </c>
+      <c r="AJ5">
+        <v>400</v>
+      </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -1321,8 +1377,14 @@
       <c r="AH6">
         <v>-237.7999999999993</v>
       </c>
+      <c r="AI6">
+        <v>350</v>
+      </c>
+      <c r="AJ6">
+        <v>400</v>
+      </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>46</v>
       </c>
@@ -1425,8 +1487,14 @@
       <c r="AH7">
         <v>-63.399999999999409</v>
       </c>
+      <c r="AI7">
+        <v>350</v>
+      </c>
+      <c r="AJ7">
+        <v>400</v>
+      </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -1529,8 +1597,14 @@
       <c r="AH8">
         <v>310.1999999999997</v>
       </c>
+      <c r="AI8">
+        <v>350</v>
+      </c>
+      <c r="AJ8">
+        <v>350</v>
+      </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -1633,8 +1707,14 @@
       <c r="AH9">
         <v>-311.0999999999998</v>
       </c>
+      <c r="AI9">
+        <v>350</v>
+      </c>
+      <c r="AJ9">
+        <v>350</v>
+      </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>52</v>
       </c>
@@ -1737,8 +1817,14 @@
       <c r="AH10">
         <v>-333.09999999999991</v>
       </c>
+      <c r="AI10">
+        <v>350</v>
+      </c>
+      <c r="AJ10">
+        <v>350</v>
+      </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -1841,8 +1927,14 @@
       <c r="AH11">
         <v>484.80000000000013</v>
       </c>
+      <c r="AI11">
+        <v>350</v>
+      </c>
+      <c r="AJ11">
+        <v>354</v>
+      </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -1945,8 +2037,14 @@
       <c r="AH12">
         <v>292.69999999999982</v>
       </c>
+      <c r="AI12">
+        <v>273</v>
+      </c>
+      <c r="AJ12">
+        <v>200</v>
+      </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>59</v>
       </c>
@@ -2049,8 +2147,14 @@
       <c r="AH13">
         <v>76.699999999999591</v>
       </c>
+      <c r="AI13">
+        <v>351</v>
+      </c>
+      <c r="AJ13">
+        <v>350</v>
+      </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>61</v>
       </c>
@@ -2153,8 +2257,14 @@
       <c r="AH14">
         <v>-231.70000000000061</v>
       </c>
+      <c r="AI14">
+        <v>350</v>
+      </c>
+      <c r="AJ14">
+        <v>350</v>
+      </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>63</v>
       </c>
@@ -2257,8 +2367,14 @@
       <c r="AH15">
         <v>-125.3000000000003</v>
       </c>
+      <c r="AI15">
+        <v>350</v>
+      </c>
+      <c r="AJ15">
+        <v>350</v>
+      </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>64</v>
       </c>
@@ -2361,8 +2477,14 @@
       <c r="AH16">
         <v>59.600000000000023</v>
       </c>
+      <c r="AI16">
+        <v>350</v>
+      </c>
+      <c r="AJ16">
+        <v>350</v>
+      </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -2465,8 +2587,14 @@
       <c r="AH17">
         <v>525.30000000000007</v>
       </c>
+      <c r="AI17">
+        <v>350</v>
+      </c>
+      <c r="AJ17">
+        <v>350</v>
+      </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -2569,8 +2697,14 @@
       <c r="AH18">
         <v>55.10000000000025</v>
       </c>
+      <c r="AI18">
+        <v>350</v>
+      </c>
+      <c r="AJ18">
+        <v>350</v>
+      </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>69</v>
       </c>
@@ -2673,8 +2807,14 @@
       <c r="AH19">
         <v>-311.0999999999998</v>
       </c>
+      <c r="AI19">
+        <v>350</v>
+      </c>
+      <c r="AJ19">
+        <v>350</v>
+      </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>70</v>
       </c>
@@ -2777,8 +2917,14 @@
       <c r="AH20">
         <v>125.3000000000003</v>
       </c>
+      <c r="AI20">
+        <v>734</v>
+      </c>
+      <c r="AJ20">
+        <v>400</v>
+      </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>71</v>
       </c>
@@ -2881,8 +3027,14 @@
       <c r="AH21">
         <v>239.90000000000069</v>
       </c>
+      <c r="AI21">
+        <v>3145</v>
+      </c>
+      <c r="AJ21">
+        <v>9340</v>
+      </c>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -2985,8 +3137,14 @@
       <c r="AH22">
         <v>-18.39999999999986</v>
       </c>
+      <c r="AI22">
+        <v>703</v>
+      </c>
+      <c r="AJ22">
+        <v>414</v>
+      </c>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -3089,8 +3247,14 @@
       <c r="AH23">
         <v>129.10000000000051</v>
       </c>
+      <c r="AI23">
+        <v>358</v>
+      </c>
+      <c r="AJ23">
+        <v>750</v>
+      </c>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -3193,8 +3357,14 @@
       <c r="AH24">
         <v>-14.99999999999932</v>
       </c>
+      <c r="AI24">
+        <v>652</v>
+      </c>
+      <c r="AJ24">
+        <v>759</v>
+      </c>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>77</v>
       </c>
@@ -3297,8 +3467,14 @@
       <c r="AH25">
         <v>-95.700000000000273</v>
       </c>
+      <c r="AI25">
+        <v>359</v>
+      </c>
+      <c r="AJ25">
+        <v>350</v>
+      </c>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>78</v>
       </c>
@@ -3401,8 +3577,14 @@
       <c r="AH26">
         <v>404.1</v>
       </c>
+      <c r="AI26">
+        <v>407</v>
+      </c>
+      <c r="AJ26">
+        <v>350</v>
+      </c>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>79</v>
       </c>
@@ -3505,8 +3687,14 @@
       <c r="AH27">
         <v>347</v>
       </c>
+      <c r="AI27">
+        <v>650</v>
+      </c>
+      <c r="AJ27">
+        <v>750</v>
+      </c>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>80</v>
       </c>
@@ -3609,8 +3797,14 @@
       <c r="AH28">
         <v>-369.00000000000108</v>
       </c>
+      <c r="AI28">
+        <v>350</v>
+      </c>
+      <c r="AJ28">
+        <v>400</v>
+      </c>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>81</v>
       </c>
@@ -3713,8 +3907,14 @@
       <c r="AH29">
         <v>-269.20000000000027</v>
       </c>
+      <c r="AI29">
+        <v>350</v>
+      </c>
+      <c r="AJ29">
+        <v>350</v>
+      </c>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>83</v>
       </c>
@@ -3817,8 +4017,14 @@
       <c r="AH30">
         <v>347</v>
       </c>
+      <c r="AI30">
+        <v>650</v>
+      </c>
+      <c r="AJ30">
+        <v>713</v>
+      </c>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>84</v>
       </c>
@@ -3921,8 +4127,14 @@
       <c r="AH31">
         <v>-8.8999999999992951</v>
       </c>
+      <c r="AI31">
+        <v>650</v>
+      </c>
+      <c r="AJ31">
+        <v>715</v>
+      </c>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>86</v>
       </c>
@@ -4025,8 +4237,14 @@
       <c r="AH32">
         <v>-62.500000000000227</v>
       </c>
+      <c r="AI32">
+        <v>350</v>
+      </c>
+      <c r="AJ32">
+        <v>350</v>
+      </c>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>87</v>
       </c>
@@ -4129,8 +4347,14 @@
       <c r="AH33">
         <v>-303.30000000000092</v>
       </c>
+      <c r="AI33">
+        <v>382</v>
+      </c>
+      <c r="AJ33">
+        <v>350</v>
+      </c>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>88</v>
       </c>
@@ -4233,8 +4457,14 @@
       <c r="AH34">
         <v>63.400000000000198</v>
       </c>
+      <c r="AI34">
+        <v>359</v>
+      </c>
+      <c r="AJ34">
+        <v>350</v>
+      </c>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>89</v>
       </c>
@@ -4337,8 +4567,14 @@
       <c r="AH35">
         <v>-244.6</v>
       </c>
+      <c r="AI35">
+        <v>350</v>
+      </c>
+      <c r="AJ35">
+        <v>400</v>
+      </c>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>90</v>
       </c>
@@ -4441,8 +4677,14 @@
       <c r="AH36">
         <v>-3.7999999999993861</v>
       </c>
+      <c r="AI36">
+        <v>650</v>
+      </c>
+      <c r="AJ36">
+        <v>1172</v>
+      </c>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>91</v>
       </c>
@@ -4545,8 +4787,14 @@
       <c r="AH37">
         <v>94.800000000000182</v>
       </c>
+      <c r="AI37">
+        <v>350</v>
+      </c>
+      <c r="AJ37">
+        <v>200</v>
+      </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>92</v>
       </c>
@@ -4650,7 +4898,7 @@
         <v>291.79999999999978</v>
       </c>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>93</v>
       </c>
@@ -4754,7 +5002,7 @@
         <v>115.8000000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>94</v>
       </c>
@@ -4858,7 +5106,7 @@
         <v>26.39999999999986</v>
       </c>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>95</v>
       </c>
@@ -4962,7 +5210,7 @@
         <v>99.300000000000068</v>
       </c>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>96</v>
       </c>
@@ -5066,7 +5314,7 @@
         <v>-42.699999999999697</v>
       </c>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>98</v>
       </c>
@@ -5170,7 +5418,7 @@
         <v>194.6000000000013</v>
       </c>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>99</v>
       </c>
@@ -5274,7 +5522,7 @@
         <v>-385.5</v>
       </c>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -5378,7 +5626,7 @@
         <v>-174.39999999999989</v>
       </c>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>101</v>
       </c>
@@ -5482,7 +5730,7 @@
         <v>-458.4000000000002</v>
       </c>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>102</v>
       </c>
@@ -5586,7 +5834,7 @@
         <v>-37.899999999999977</v>
       </c>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>103</v>
       </c>
